--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conda/Desktop/site/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F63458-928B-1B4E-8D43-CFE7D43D00F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F2054C-99AA-234B-BCB4-80A189368910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="34200" windowHeight="20300" xr2:uid="{A3F9586F-1F18-5E42-AD7E-A6AA1523E0B6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="304">
   <si>
     <t>2011-01</t>
   </si>
@@ -945,6 +945,9 @@
   </si>
   <si>
     <t>2010-12</t>
+  </si>
+  <si>
+    <t>2026-04</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A417241-3E0E-EA4C-B426-2A149AE30B52}">
-  <dimension ref="A1:F292"/>
+  <dimension ref="A1:F295"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -6371,7 +6374,7 @@
         <v>0.4</v>
       </c>
       <c r="C291" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D291" s="2">
         <v>6.45</v>
@@ -6391,7 +6394,7 @@
         <v>0.4</v>
       </c>
       <c r="C292" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D292" s="2">
         <v>6.09</v>
@@ -6402,6 +6405,37 @@
       <c r="F292">
         <v>3.4</v>
       </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A293" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B293" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="C293" s="2">
+        <v>7</v>
+      </c>
+      <c r="D293" s="2">
+        <v>5.83</v>
+      </c>
+      <c r="E293" s="2">
+        <v>5.47</v>
+      </c>
+      <c r="F293" s="2">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
+      <c r="E294" s="2"/>
+      <c r="F294" s="2"/>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
+      <c r="E295" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
